--- a/templates/今日_Cafre_Global_Markets_Update/scripts.xlsx
+++ b/templates/今日_Cafre_Global_Markets_Update/scripts.xlsx
@@ -446,36 +446,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Stop Kena SL Gara-gara Candle Palsu</t>
+          <t>Rupee Falls to 96.42 Against the US Dollar</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pernah nggak? Lihat candlestick Shooting Star, langsung Sell. Eh, malah kena Stop Loss dulu. Baru setelah itu harga benar-benar jatuh. Kok bisa?
-Masalahnya, jangan percaya bentuk candlestick doang.
-Semakin banyak candle yang membentuk pola reversal, biasanya sinyalnya makin kuat.
-Satu candle? Masih rawan fakeout.
-Dua candle seperti Engulfing? Lebih meyakinkan.
-Tiga candle seperti Morning Star atau Evening Star? Konfirmasinya jauh lebih matang.
-Tapi itu belum cukup.
-Pola reversal cuma layak dipakai kalau muncul di area support atau resistance yang kuat, dan wajib tunggu candle benar-benar close. Jangan entry saat candle masih berjalan.
-Terakhir, pastikan juga broker yang kamu pakai punya spread yang wajar. Karena spread yang melebar bisa bikin sinyal bagus berubah jadi jebakan.
-Follow WikiFX buat belajar trading lebih cerdas dan cek dulu skor broker sebelum deposit.</t>
+          <t>The Indian rupee has weakened again! But should you be worried?
+The Indian rupee slipped by 6 paise to 96.42 against the U.S. dollar in early trading.
+So, what's behind this fall?
+Rising geopolitical tensions have increased demand for the U.S. dollar, which is considered a safe-haven currency.
+Crude oil prices remain elevated, and since India imports most of its oil, a stronger dollar makes those imports more expensive.
+Foreign investors also continued selling Indian equities, adding further pressure on the rupee.
+The dollar index is hovering around 100.97, while traders are closely monitoring developments in West Asia that could impact global oil supplies.
+A weaker rupee can increase the cost of imports and overseas travel, but it may also benefit export-oriented businesses.
+Do you think the rupee will recover soon, or could it weaken further? Share your thoughts in the comments.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Analisis candlestick pola reversal forex support resistance spread broker</t>
+          <t>Indian rupee 96.42 US dollar geopolitical tension safe haven crude oil imports foreign investors selling equities dollar index West Asia</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ANALISIS FOREX</t>
+          <t>FOREX MARKET NEWS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>en</t>
         </is>
       </c>
     </row>
